--- a/InputData/trans/BNoGP/BAU Number of Gas Pumps.xlsx
+++ b/InputData/trans/BNoGP/BAU Number of Gas Pumps.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreazafra/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\Mexico EPS\InputData\trans\BNoGP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4FDEC9-356F-8246-9B96-074570D93CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B732D1B-93F6-40E7-8140-32335FB531E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31020" yWindow="3740" windowWidth="28580" windowHeight="15460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37050" yWindow="1065" windowWidth="22785" windowHeight="14115" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -157,7 +157,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -174,6 +174,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -456,18 +457,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.5" customWidth="1"/>
-    <col min="2" max="2" width="31.83203125" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" customWidth="1"/>
+    <col min="2" max="2" width="31.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -475,32 +476,32 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -514,9 +515,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB811F65-9F20-D140-A7B1-D6BBDE3C3CF4}">
   <dimension ref="A1:R3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B1" s="6" t="s">
         <v>13</v>
       </c>
@@ -539,7 +540,7 @@
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -595,7 +596,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -665,14 +666,14 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AZ3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -827,211 +828,263 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="8">
         <f>'Hist data'!D3</f>
         <v>12884</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="8">
         <f>'Hist data'!E3</f>
         <v>13389</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="8">
         <f>'Hist data'!F3</f>
         <v>13633</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="8">
         <f>'Hist data'!G3</f>
         <v>13837</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="8">
         <f>'Hist data'!H3</f>
         <v>14111.2</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="8">
         <f>'Hist data'!I3</f>
         <v>14375.4</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="8">
         <f>'Hist data'!J3</f>
         <v>14639.6</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="8">
         <f>'Hist data'!K3</f>
         <v>14903.8</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="8">
         <f>'Hist data'!L3</f>
         <v>15168</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="8">
         <f>'Hist data'!M3</f>
         <v>15432.2</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="8">
         <f>'Hist data'!N3</f>
         <v>15696.4</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="8">
         <f>'Hist data'!O3</f>
         <v>15960.6</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="8">
         <f>'Hist data'!P3</f>
         <v>16224.8</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="8">
         <f>'Hist data'!Q3</f>
         <v>16489</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="8">
         <f>'Hist data'!R3</f>
         <v>16753.2</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="8">
         <f>P2</f>
         <v>16753.2</v>
       </c>
-      <c r="R2" s="5">
-        <f t="shared" ref="R2:AZ2" si="0">Q2</f>
-        <v>16753.2</v>
-      </c>
-      <c r="S2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="T2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="U2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="V2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="W2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="X2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="Y2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="Z2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AA2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AB2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AC2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AD2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AE2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AF2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AG2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AH2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AI2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AJ2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AK2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AL2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AM2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AN2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AO2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AP2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AQ2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AR2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AS2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AT2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AU2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AV2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AW2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AX2" s="5">
-        <f t="shared" si="0"/>
-        <v>16753.2</v>
-      </c>
-      <c r="AY2" s="5">
+      <c r="R2" s="8">
+        <f t="shared" ref="R2:AY2" si="0">Q2</f>
+        <v>16753.2</v>
+      </c>
+      <c r="S2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="T2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="U2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="V2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="W2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="X2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="Y2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="Z2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AA2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AB2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AC2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AD2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AE2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AF2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AG2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AH2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AI2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AJ2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AK2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AL2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AM2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AN2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AO2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AP2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AQ2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AR2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AS2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AT2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AU2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AV2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AW2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AX2" s="8">
+        <f t="shared" si="0"/>
+        <v>16753.2</v>
+      </c>
+      <c r="AY2" s="8">
         <f t="shared" si="0"/>
         <v>16753.2</v>
       </c>
       <c r="AZ2" s="5"/>
+    </row>
+    <row r="3" spans="1:52" x14ac:dyDescent="0.3">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="8"/>
+      <c r="W3" s="8"/>
+      <c r="X3" s="8"/>
+      <c r="Y3" s="8"/>
+      <c r="Z3" s="8"/>
+      <c r="AA3" s="8"/>
+      <c r="AB3" s="8"/>
+      <c r="AC3" s="8"/>
+      <c r="AD3" s="8"/>
+      <c r="AE3" s="8"/>
+      <c r="AF3" s="8"/>
+      <c r="AG3" s="8"/>
+      <c r="AH3" s="8"/>
+      <c r="AI3" s="8"/>
+      <c r="AJ3" s="8"/>
+      <c r="AK3" s="8"/>
+      <c r="AL3" s="8"/>
+      <c r="AM3" s="8"/>
+      <c r="AN3" s="8"/>
+      <c r="AO3" s="8"/>
+      <c r="AP3" s="8"/>
+      <c r="AQ3" s="8"/>
+      <c r="AR3" s="8"/>
+      <c r="AS3" s="8"/>
+      <c r="AT3" s="8"/>
+      <c r="AU3" s="8"/>
+      <c r="AV3" s="8"/>
+      <c r="AW3" s="8"/>
+      <c r="AX3" s="8"/>
+      <c r="AY3" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1039,9 +1092,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1189,19 +1245,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B17D107-A6C5-491E-A74E-1FE4C658B85E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9139C56C-C4C4-4C76-9FCD-364FA7D09879}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1225,9 +1277,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9139C56C-C4C4-4C76-9FCD-364FA7D09879}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B17D107-A6C5-491E-A74E-1FE4C658B85E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>